--- a/data/trans_camb/IP16A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 29,51</t>
+          <t>-20,56; 29,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,33; 19,06</t>
+          <t>-24,93; 20,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 48,38</t>
+          <t>-0,43; 47,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 0,58</t>
+          <t>-50,15; -1,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,76; -2,68</t>
+          <t>-47,79; -3,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 26,78</t>
+          <t>-19,67; 30,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 4,04</t>
+          <t>-28,78; 6,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,71; -1,21</t>
+          <t>-34,84; -1,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 31,1</t>
+          <t>-4,98; 28,99</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 189,51</t>
+          <t>-48,04; 177,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,26; 105,48</t>
+          <t>-59,53; 121,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 281,52</t>
+          <t>-1,99; 287,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,84; 1,56</t>
+          <t>-74,8; -2,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,12; -5,15</t>
+          <t>-72,88; -4,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 68,19</t>
+          <t>-28,37; 73,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 10,54</t>
+          <t>-52,97; 18,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,93; -0,33</t>
+          <t>-64,02; -3,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 91,61</t>
+          <t>-8,82; 79,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 22,92</t>
+          <t>-25,04; 22,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 25,95</t>
+          <t>-21,0; 27,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 32,52</t>
+          <t>-19,42; 29,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 33,0</t>
+          <t>-23,25; 34,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 31,78</t>
+          <t>-22,22; 27,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 31,33</t>
+          <t>-19,88; 31,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 20,51</t>
+          <t>-16,05; 21,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 21,46</t>
+          <t>-14,51; 21,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 24,02</t>
+          <t>-12,62; 23,78</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-45,34; 82,58</t>
+          <t>-50,24; 81,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,15; 100,18</t>
+          <t>-41,37; 105,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 127,05</t>
+          <t>-34,88; 112,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,65; 129,69</t>
+          <t>-44,77; 129,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,25; 134,35</t>
+          <t>-40,02; 109,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 123,42</t>
+          <t>-39,44; 114,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,43; 67,62</t>
+          <t>-33,05; 71,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,1; 69,86</t>
+          <t>-29,62; 65,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 74,08</t>
+          <t>-25,28; 75,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,27; 41,77</t>
+          <t>-19,24; 42,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-34,2; 31,01</t>
+          <t>-35,92; 30,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 45,67</t>
+          <t>-27,09; 42,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 52,0</t>
+          <t>4,24; 54,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 48,61</t>
+          <t>-8,77; 50,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 30,07</t>
+          <t>-22,92; 30,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 39,96</t>
+          <t>3,72; 41,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 32,43</t>
+          <t>-7,16; 33,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 26,56</t>
+          <t>-14,35; 24,43</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 190,13</t>
+          <t>-32,2; 196,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,64; 147,12</t>
+          <t>-60,82; 122,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 212,22</t>
+          <t>-46,3; 185,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,74; 245,63</t>
+          <t>9,99; 276,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 231,48</t>
+          <t>-21,8; 231,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,05; 134,11</t>
+          <t>-50,11; 137,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 155,12</t>
+          <t>7,46; 160,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 123,22</t>
+          <t>-17,64; 126,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 102,16</t>
+          <t>-31,22; 98,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 19,74</t>
+          <t>-10,98; 22,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 24,54</t>
+          <t>-7,76; 24,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 16,58</t>
+          <t>-36,0; 20,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 6,34</t>
+          <t>-24,24; 6,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 7,65</t>
+          <t>-28,58; 7,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 11,14</t>
+          <t>-22,57; 11,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 9,63</t>
+          <t>-14,22; 9,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 10,91</t>
+          <t>-12,56; 10,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 8,48</t>
+          <t>-24,15; 10,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,34; 84,25</t>
+          <t>-26,15; 101,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 106,23</t>
+          <t>-18,43; 111,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 55,66</t>
+          <t>-74,76; 66,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 16,66</t>
+          <t>-44,92; 17,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 23,99</t>
+          <t>-53,35; 20,71</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 30,4</t>
+          <t>-42,67; 32,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,76; 30,12</t>
+          <t>-30,92; 28,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 34,46</t>
+          <t>-28,18; 31,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 22,71</t>
+          <t>-54,74; 28,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 36,87</t>
+          <t>-9,13; 35,25</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 32,64</t>
+          <t>-14,87; 30,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 40,59</t>
+          <t>-5,73; 40,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 29,92</t>
+          <t>-16,69; 25,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 16,67</t>
+          <t>-28,63; 15,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 21,05</t>
+          <t>-21,78; 19,94</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 24,1</t>
+          <t>-5,09; 24,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 17,27</t>
+          <t>-13,0; 15,86</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 24,25</t>
+          <t>-6,74; 24,06</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 249,26</t>
+          <t>-22,07; 210,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,53; 219,35</t>
+          <t>-32,2; 192,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 256,99</t>
+          <t>-14,47; 238,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 118,04</t>
+          <t>-35,93; 98,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,8; 60,93</t>
+          <t>-56,17; 58,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 77,9</t>
+          <t>-42,84; 73,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-14,95; 90,92</t>
+          <t>-11,81; 95,6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 68,29</t>
+          <t>-30,58; 60,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 99,18</t>
+          <t>-16,49; 94,72</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 68,47</t>
+          <t>-1,14; 68,1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-42,34; 23,88</t>
+          <t>-43,93; 21,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-29,59; 45,13</t>
+          <t>-26,16; 44,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 26,56</t>
+          <t>-27,74; 29,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 35,41</t>
+          <t>-25,8; 33,95</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 40,58</t>
+          <t>-19,07; 45,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 39,68</t>
+          <t>-8,32; 38,36</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 19,89</t>
+          <t>-24,41; 18,7</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 34,7</t>
+          <t>-11,01; 35,65</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 677,65</t>
+          <t>-2,4; 769,18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-79,63; 216,6</t>
+          <t>-82,8; 212,61</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 436,17</t>
+          <t>-46,61; 423,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-72,79; 228,69</t>
+          <t>-70,89; 287,26</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-63,99; 273,27</t>
+          <t>-63,27; 270,38</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-48,03; 310,71</t>
+          <t>-46,45; 379,81</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 235,56</t>
+          <t>-17,34; 215,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 112,29</t>
+          <t>-58,11; 108,07</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 221,0</t>
+          <t>-23,49; 210,91</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 18,75</t>
+          <t>-0,22; 19,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 14,24</t>
+          <t>-6,64; 13,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 18,67</t>
+          <t>-11,66; 17,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 7,01</t>
+          <t>-11,23; 6,74</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 4,07</t>
+          <t>-13,33; 4,9</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 11,6</t>
+          <t>-7,5; 11,8</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 9,8</t>
+          <t>-2,75; 10,03</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 5,34</t>
+          <t>-7,07; 5,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 11,58</t>
+          <t>-7,49; 11,51</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 65,4</t>
+          <t>-1,56; 68,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 49,15</t>
+          <t>-16,18; 46,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-27,82; 59,75</t>
+          <t>-28,05; 55,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,37; 19,44</t>
+          <t>-24,35; 18,15</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,01; 11,09</t>
+          <t>-29,57; 13,89</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 30,75</t>
+          <t>-16,4; 33,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 27,53</t>
+          <t>-6,83; 27,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 15,24</t>
+          <t>-16,78; 16,61</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 33,03</t>
+          <t>-17,63; 31,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 29,1</t>
+          <t>-19,04; 28,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-24,93; 20,05</t>
+          <t>-27,21; 18,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 47,71</t>
+          <t>-0,28; 46,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-50,15; -1,79</t>
+          <t>-47,39; -3,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,79; -3,89</t>
+          <t>-47,48; -0,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,67; 30,98</t>
+          <t>-18,07; 27,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,78; 6,07</t>
+          <t>-28,81; 5,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,84; -1,28</t>
+          <t>-35,44; -1,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 28,99</t>
+          <t>-5,26; 31,0</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 177,64</t>
+          <t>-43,32; 162,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,53; 121,99</t>
+          <t>-63,39; 119,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 287,35</t>
+          <t>1,32; 280,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-74,8; -2,76</t>
+          <t>-72,58; -4,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,88; -4,91</t>
+          <t>-72,03; -0,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,37; 73,49</t>
+          <t>-26,62; 70,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 18,16</t>
+          <t>-51,99; 17,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-64,02; -3,23</t>
+          <t>-63,8; -0,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 79,82</t>
+          <t>-11,13; 87,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,04; 22,19</t>
+          <t>-22,66; 23,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 27,86</t>
+          <t>-22,72; 28,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 29,44</t>
+          <t>-17,96; 31,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-23,25; 34,33</t>
+          <t>-20,98; 30,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 27,43</t>
+          <t>-22,2; 31,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 31,77</t>
+          <t>-21,36; 32,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 21,25</t>
+          <t>-17,05; 20,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 21,52</t>
+          <t>-13,5; 22,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 23,78</t>
+          <t>-12,03; 22,68</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 81,35</t>
+          <t>-43,64; 106,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 105,92</t>
+          <t>-43,6; 109,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 112,13</t>
+          <t>-33,47; 128,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,77; 129,41</t>
+          <t>-41,31; 111,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,02; 109,4</t>
+          <t>-40,63; 114,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,44; 114,8</t>
+          <t>-39,18; 132,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,05; 71,97</t>
+          <t>-34,01; 69,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 65,42</t>
+          <t>-26,93; 72,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-25,28; 75,77</t>
+          <t>-24,26; 76,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,24; 42,77</t>
+          <t>-21,21; 42,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 30,59</t>
+          <t>-31,74; 32,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 42,89</t>
+          <t>-28,99; 41,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,24; 54,35</t>
+          <t>3,52; 51,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 50,05</t>
+          <t>-5,07; 52,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 30,48</t>
+          <t>-20,63; 33,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 41,51</t>
+          <t>2,55; 40,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 33,97</t>
+          <t>-8,05; 35,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 24,43</t>
+          <t>-14,61; 29,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 196,97</t>
+          <t>-36,27; 190,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,82; 122,87</t>
+          <t>-57,21; 136,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,3; 185,25</t>
+          <t>-51,38; 163,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,99; 276,75</t>
+          <t>1,3; 232,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 231,78</t>
+          <t>-14,96; 227,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,11; 137,38</t>
+          <t>-50,77; 153,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,46; 160,26</t>
+          <t>3,84; 157,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 126,27</t>
+          <t>-20,03; 131,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 98,07</t>
+          <t>-32,57; 116,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 22,93</t>
+          <t>-11,2; 19,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 24,58</t>
+          <t>-7,74; 25,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 20,22</t>
+          <t>-32,16; 19,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 6,25</t>
+          <t>-24,45; 7,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-28,58; 7,05</t>
+          <t>-27,23; 5,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 11,61</t>
+          <t>-22,58; 12,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 9,15</t>
+          <t>-13,43; 10,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 10,61</t>
+          <t>-12,21; 10,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 10,05</t>
+          <t>-27,39; 8,21</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 101,28</t>
+          <t>-26,17; 86,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 111,51</t>
+          <t>-18,39; 111,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,76; 66,63</t>
+          <t>-72,12; 67,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,92; 17,87</t>
+          <t>-45,56; 20,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 20,71</t>
+          <t>-52,15; 15,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 32,35</t>
+          <t>-43,56; 34,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,92; 28,31</t>
+          <t>-28,72; 32,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,18; 31,84</t>
+          <t>-27,61; 33,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,74; 28,06</t>
+          <t>-61,37; 21,93</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 35,25</t>
+          <t>-8,48; 35,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 30,52</t>
+          <t>-15,05; 30,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 40,38</t>
+          <t>-6,41; 41,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 25,93</t>
+          <t>-16,91; 27,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 15,21</t>
+          <t>-26,91; 16,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 19,94</t>
+          <t>-22,81; 20,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 24,16</t>
+          <t>-5,95; 24,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 15,86</t>
+          <t>-14,0; 17,54</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 24,06</t>
+          <t>-7,99; 22,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 210,3</t>
+          <t>-18,72; 216,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,2; 192,66</t>
+          <t>-32,67; 182,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 238,57</t>
+          <t>-14,16; 282,92</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,93; 98,46</t>
+          <t>-31,18; 113,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,17; 58,96</t>
+          <t>-52,84; 62,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 73,2</t>
+          <t>-46,04; 79,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 95,6</t>
+          <t>-12,83; 99,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-30,58; 60,57</t>
+          <t>-32,15; 67,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 94,72</t>
+          <t>-18,57; 89,8</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 68,1</t>
+          <t>-1,49; 69,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-43,93; 21,73</t>
+          <t>-44,49; 20,54</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-26,16; 44,87</t>
+          <t>-25,96; 42,28</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-27,74; 29,47</t>
+          <t>-28,32; 28,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,8; 33,95</t>
+          <t>-24,8; 39,66</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 45,87</t>
+          <t>-19,1; 45,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 38,36</t>
+          <t>-7,75; 37,93</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 18,7</t>
+          <t>-25,41; 19,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 35,65</t>
+          <t>-12,36; 33,17</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 769,18</t>
+          <t>-3,88; 752,48</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-82,8; 212,61</t>
+          <t>-80,58; 188,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 423,47</t>
+          <t>-49,63; 462,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-70,89; 287,26</t>
+          <t>-67,08; 278,07</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 270,38</t>
+          <t>-57,95; 380,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-46,45; 379,81</t>
+          <t>-42,38; 410,52</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 215,78</t>
+          <t>-18,21; 213,05</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-58,11; 108,07</t>
+          <t>-58,18; 104,65</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 210,91</t>
+          <t>-29,07; 184,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 19,54</t>
+          <t>-1,26; 17,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 13,11</t>
+          <t>-6,17; 12,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 17,74</t>
+          <t>-12,46; 19,01</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 6,74</t>
+          <t>-11,92; 7,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,33; 4,9</t>
+          <t>-15,18; 4,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 11,8</t>
+          <t>-6,6; 11,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 10,03</t>
+          <t>-3,51; 10,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 5,68</t>
+          <t>-7,01; 6,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 11,51</t>
+          <t>-8,36; 11,15</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 68,2</t>
+          <t>-3,08; 60,83</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 46,08</t>
+          <t>-15,76; 43,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-28,05; 55,99</t>
+          <t>-31,42; 61,25</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 18,15</t>
+          <t>-24,87; 19,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 13,89</t>
+          <t>-32,37; 11,95</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 33,34</t>
+          <t>-14,72; 32,44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 27,69</t>
+          <t>-8,36; 29,13</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 16,61</t>
+          <t>-17,05; 18,1</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 31,63</t>
+          <t>-18,79; 31,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A02-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16A02-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-25,82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-25,96</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,22</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,07</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-4,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24,89</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-25,82</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-25,96</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,93</t>
+          <t>24,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13,07</t>
+          <t>13,02</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 28,69</t>
+          <t>-47,98; 0,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 18,92</t>
+          <t>-47,76; -2,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 46,12</t>
+          <t>-18,24; 27,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-47,39; -3,21</t>
+          <t>-20,18; 29,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-47,48; -0,02</t>
+          <t>-28,33; 19,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 27,32</t>
+          <t>-1,55; 48,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 5,24</t>
+          <t>-30,93; 4,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,44; -1,3</t>
+          <t>-35,71; -1,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 31,0</t>
+          <t>-3,36; 31,18</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-45,97%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-46,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,29%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>16,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-14,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>78,49%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-45,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-46,23%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,32; 162,7</t>
+          <t>-72,84; 1,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 119,8</t>
+          <t>-74,12; -5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 280,67</t>
+          <t>-27,27; 68,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-72,58; -4,62</t>
+          <t>-47,26; 189,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-72,03; -0,04</t>
+          <t>-64,26; 105,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 70,47</t>
+          <t>-2,1; 279,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 17,11</t>
+          <t>-54,75; 10,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-63,8; -0,7</t>
+          <t>-63,93; -0,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 87,11</t>
+          <t>-6,31; 90,06</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,23</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,99</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,14</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,05</t>
+          <t>8,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6,05</t>
+          <t>6,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 23,77</t>
+          <t>-23,76; 33,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 28,5</t>
+          <t>-18,71; 31,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,96; 31,83</t>
+          <t>-19,06; 31,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 30,93</t>
+          <t>-23,43; 22,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 31,03</t>
+          <t>-24,18; 25,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 32,96</t>
+          <t>-17,89; 33,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 20,96</t>
+          <t>-15,87; 20,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 22,29</t>
+          <t>-14,43; 21,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 22,68</t>
+          <t>-12,36; 24,75</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>7,38%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17,37%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-43,64; 106,93</t>
+          <t>-44,65; 129,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,6; 109,38</t>
+          <t>-37,25; 134,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 128,63</t>
+          <t>-36,62; 127,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 111,53</t>
+          <t>-45,34; 82,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 114,28</t>
+          <t>-46,15; 100,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 132,59</t>
+          <t>-32,74; 128,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 69,3</t>
+          <t>-32,43; 67,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,93; 72,93</t>
+          <t>-29,1; 69,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 76,05</t>
+          <t>-23,86; 76,19</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30,18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22,4</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,22</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>11,26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,41</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,11</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>22,4</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,4</t>
+          <t>11,41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>8,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-21,21; 42,93</t>
+          <t>2,53; 52,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 32,97</t>
+          <t>-4,6; 48,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,99; 41,19</t>
+          <t>-21,4; 32,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,52; 51,94</t>
+          <t>-19,27; 41,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 52,3</t>
+          <t>-34,2; 31,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 33,29</t>
+          <t>-18,33; 48,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,55; 40,76</t>
+          <t>3,11; 39,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 35,52</t>
+          <t>-8,64; 32,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 29,44</t>
+          <t>-11,88; 29,24</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>91,08%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>67,6%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18,76%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>26,72%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-0,97%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19,24%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>91,08%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 190,12</t>
+          <t>3,74; 245,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 136,9</t>
+          <t>-11,28; 231,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,38; 163,74</t>
+          <t>-51,63; 145,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 232,84</t>
+          <t>-34,49; 190,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 227,6</t>
+          <t>-62,64; 147,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,77; 153,22</t>
+          <t>-35,26; 220,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,84; 157,98</t>
+          <t>5,99; 155,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 131,89</t>
+          <t>-18,93; 123,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 116,64</t>
+          <t>-26,45; 109,4</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-8,92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-11,32</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-7,19</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>8,64</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-4,59</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-8,92</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-11,32</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-4,62</t>
+          <t>13,23</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,59</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 19,44</t>
+          <t>-25,54; 6,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 25,0</t>
+          <t>-28,87; 7,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 19,53</t>
+          <t>-26,77; 8,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 7,27</t>
+          <t>-11,65; 19,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 5,83</t>
+          <t>-8,24; 24,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 12,12</t>
+          <t>-5,63; 30,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 10,21</t>
+          <t>-12,73; 9,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 10,82</t>
+          <t>-13,41; 10,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 8,21</t>
+          <t>-10,62; 14,57</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-19,9%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-25,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-16,03%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>15,33%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>25,98%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-13,82%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-19,9%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-25,24%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,3%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,28%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 86,56</t>
+          <t>-47,17; 16,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 111,58</t>
+          <t>-54,74; 23,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,12; 67,45</t>
+          <t>-50,71; 21,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 20,32</t>
+          <t>-28,34; 84,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-52,15; 15,03</t>
+          <t>-19,78; 106,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,56; 34,15</t>
+          <t>-13,62; 118,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 32,31</t>
+          <t>-28,76; 30,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,61; 33,53</t>
+          <t>-29,61; 34,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,37; 21,93</t>
+          <t>-22,72; 42,92</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,56</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-5,8</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,6</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>15,63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>9,77</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>18,42</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-5,8</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>18,71</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>9,41</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 35,34</t>
+          <t>-15,93; 29,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 30,53</t>
+          <t>-25,25; 16,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 41,44</t>
+          <t>-21,87; 23,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 27,33</t>
+          <t>-8,37; 36,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 16,24</t>
+          <t>-12,48; 32,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,81; 20,67</t>
+          <t>-5,99; 41,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 24,66</t>
+          <t>-6,03; 24,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 17,54</t>
+          <t>-14,0; 17,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 22,91</t>
+          <t>-6,21; 25,52</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-14,97%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4,13%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>51,21%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>32,01%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>60,35%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14,35%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-14,97%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,72; 216,7</t>
+          <t>-32,03; 118,04</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,67; 182,48</t>
+          <t>-52,8; 60,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 282,92</t>
+          <t>-44,09; 83,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 113,29</t>
+          <t>-18,57; 249,26</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 62,68</t>
+          <t>-29,53; 219,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 79,69</t>
+          <t>-13,41; 260,76</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 99,66</t>
+          <t>-14,95; 90,92</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 67,44</t>
+          <t>-32,56; 68,29</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 89,8</t>
+          <t>-15,52; 101,92</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,17</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5,65</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14,45</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>36,39</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-11,01</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>10,32</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,17</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,65</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,77</t>
+          <t>10,82</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>13,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 69,2</t>
+          <t>-30,84; 26,56</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 20,54</t>
+          <t>-25,02; 35,41</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-25,96; 42,28</t>
+          <t>-18,82; 41,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 28,87</t>
+          <t>-3,83; 68,47</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 39,66</t>
+          <t>-42,34; 23,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 45,97</t>
+          <t>-29,32; 44,96</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 37,93</t>
+          <t>-7,59; 39,68</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 19,07</t>
+          <t>-24,63; 19,89</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 33,17</t>
+          <t>-10,81; 36,47</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-0,58%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>49,54%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>104,49%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-31,62%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>29,64%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-0,58%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 752,48</t>
+          <t>-72,79; 228,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-80,58; 188,87</t>
+          <t>-63,99; 273,27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 462,47</t>
+          <t>-46,83; 312,91</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-67,08; 278,07</t>
+          <t>-7,5; 677,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,95; 380,49</t>
+          <t>-79,63; 216,6</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-42,38; 410,52</t>
+          <t>-52,19; 433,93</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 213,05</t>
+          <t>-17,02; 235,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-58,18; 104,65</t>
+          <t>-58,41; 112,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 184,22</t>
+          <t>-27,5; 221,52</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,95</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-5,11</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2,43</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>8,8</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>3,53</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5,96</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,95</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-5,11</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>14,67</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>7,99</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 17,67</t>
+          <t>-11,27; 7,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 12,93</t>
+          <t>-15,22; 4,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 19,01</t>
+          <t>-8,49; 11,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 7,0</t>
+          <t>-0,45; 18,75</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 4,45</t>
+          <t>-5,13; 14,24</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 11,89</t>
+          <t>3,99; 24,9</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 10,18</t>
+          <t>-3,68; 9,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 6,3</t>
+          <t>-8,19; 5,34</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 11,15</t>
+          <t>0,79; 15,18</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-4,66%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-12,2%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>25,28%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>10,14%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>17,11%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-4,66%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-12,2%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 60,83</t>
+          <t>-24,37; 19,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,76; 43,91</t>
+          <t>-32,01; 11,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 61,25</t>
+          <t>-17,56; 31,02</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 19,17</t>
+          <t>-0,97; 65,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 11,95</t>
+          <t>-13,04; 49,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 32,44</t>
+          <t>9,95; 84,98</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 29,13</t>
+          <t>-8,73; 27,53</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 18,1</t>
+          <t>-19,46; 15,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 31,25</t>
+          <t>1,93; 43,8</t>
         </is>
       </c>
     </row>
